--- a/data/gravel/Felt Breed FRD UN1TD LE 2025.xlsx
+++ b/data/gravel/Felt Breed FRD UN1TD LE 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B63E37C6-EE13-1C45-8076-C14C4105329E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{204C3206-D0DB-0D48-BCB3-FC10FBC186E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4160" yWindow="500" windowWidth="24640" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="97">
   <si>
     <t>brand</t>
   </si>
@@ -305,9 +305,6 @@
     <t>Felt</t>
   </si>
   <si>
-    <t>https://www.feltbicycles.com/en-us/bikes/gravel-adventurebikes/breed-carbon/breed-advanced-grx820.color.00879A.html</t>
-  </si>
-  <si>
     <t>threaded</t>
   </si>
   <si>
@@ -321,6 +318,12 @@
   </si>
   <si>
     <t>a8:h32</t>
+  </si>
+  <si>
+    <t>https://www.feltbicycles.com/en-us/bikes/gravel-adventurebikes/breed-carbon/breed-frd-un1td-lesramredxploraxs.color.302D29EEE7E1.html</t>
+  </si>
+  <si>
+    <t>https://azwecdnepstoragewebsiteuploads.azureedge.net/PHO_BIKE_90_RE_FELT-25-BREED-UN1TD-LE-RED-XPLOR_%23SALL_%23AEPI_%23V1.jpg</t>
   </si>
 </sst>
 </file>
@@ -692,7 +695,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -716,7 +719,12 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>90</v>
+        <v>95</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="B6" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -724,7 +732,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -1273,7 +1281,7 @@
     </row>
     <row r="31" spans="1:8">
       <c r="A31" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C31">
         <f>C33*2.54</f>
@@ -1302,7 +1310,7 @@
     </row>
     <row r="32" spans="1:8">
       <c r="A32" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C32">
         <f>C34*2.54</f>
@@ -1477,7 +1485,7 @@
         <v>43</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="50" spans="1:2">

--- a/data/gravel/Felt Breed FRD UN1TD LE 2025.xlsx
+++ b/data/gravel/Felt Breed FRD UN1TD LE 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{204C3206-D0DB-0D48-BCB3-FC10FBC186E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65AE8C9C-C4B8-C14D-A292-7C761C4F3579}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4160" yWindow="500" windowWidth="24640" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="100">
   <si>
     <t>brand</t>
   </si>
@@ -324,6 +324,15 @@
   </si>
   <si>
     <t>https://azwecdnepstoragewebsiteuploads.azureedge.net/PHO_BIKE_90_RE_FELT-25-BREED-UN1TD-LE-RED-XPLOR_%23SALL_%23AEPI_%23V1.jpg</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>Rancho Santa Margarita, California, USA</t>
+  </si>
+  <si>
+    <t>USD</t>
   </si>
 </sst>
 </file>
@@ -676,7 +685,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I72"/>
+  <dimension ref="A1:I73"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1628,7 +1637,17 @@
       <c r="A72" t="s">
         <v>66</v>
       </c>
-      <c r="B72" s="1"/>
+      <c r="B72" s="1" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2">
+      <c r="A73" t="s">
+        <v>97</v>
+      </c>
+      <c r="B73" t="s">
+        <v>98</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/gravel/Felt Breed FRD UN1TD LE 2025.xlsx
+++ b/data/gravel/Felt Breed FRD UN1TD LE 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65AE8C9C-C4B8-C14D-A292-7C761C4F3579}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD3C2BB7-C708-634D-BD09-C546C6497D8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4160" yWindow="500" windowWidth="24640" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="106">
   <si>
     <t>brand</t>
   </si>
@@ -333,6 +333,24 @@
   </si>
   <si>
     <t>USD</t>
+  </si>
+  <si>
+    <t>head_tube_d</t>
+  </si>
+  <si>
+    <t>headset_upper</t>
+  </si>
+  <si>
+    <t>headset_lower</t>
+  </si>
+  <si>
+    <t>fork_steerer</t>
+  </si>
+  <si>
+    <t>fork_steerer_d</t>
+  </si>
+  <si>
+    <t>fork_material</t>
   </si>
 </sst>
 </file>
@@ -685,7 +703,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I73"/>
+  <dimension ref="A1:I79"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1491,161 +1509,191 @@
     </row>
     <row r="49" spans="1:2">
       <c r="A49" t="s">
-        <v>43</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" t="s">
-        <v>44</v>
-      </c>
-      <c r="B50" s="1"/>
+        <v>101</v>
+      </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>45</v>
-      </c>
-      <c r="B51">
-        <v>30.9</v>
+        <v>102</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" t="s">
-        <v>46</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>74</v>
+        <v>103</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" t="s">
-        <v>47</v>
+        <v>104</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" t="s">
-        <v>48</v>
+        <v>105</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" t="s">
-        <v>49</v>
+        <v>43</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" t="s">
-        <v>50</v>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="B56" s="1"/>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" t="s">
-        <v>51</v>
+        <v>45</v>
+      </c>
+      <c r="B57">
+        <v>30.9</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" t="s">
-        <v>52</v>
-      </c>
-      <c r="B58" s="1"/>
+        <v>46</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" t="s">
-        <v>53</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>73</v>
+        <v>47</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">
-        <v>54</v>
-      </c>
-      <c r="B60" s="1"/>
+        <v>48</v>
+      </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" t="s">
-        <v>56</v>
-      </c>
-      <c r="B62">
-        <v>3</v>
+        <v>50</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" t="s">
-        <v>57</v>
-      </c>
-      <c r="B63">
-        <v>1</v>
+        <v>51</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" t="s">
-        <v>58</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="B64" s="1"/>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" t="s">
-        <v>59</v>
-      </c>
-      <c r="B65" s="1"/>
+        <v>53</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="B66" s="1"/>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" t="s">
-        <v>62</v>
-      </c>
-      <c r="B68" s="1"/>
+        <v>56</v>
+      </c>
+      <c r="B68">
+        <v>3</v>
+      </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" t="s">
-        <v>63</v>
-      </c>
-      <c r="B69" s="1"/>
+        <v>57</v>
+      </c>
+      <c r="B69">
+        <v>1</v>
+      </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" t="s">
-        <v>64</v>
-      </c>
-      <c r="B70">
-        <v>11999</v>
+        <v>58</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="B71" s="1"/>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" t="s">
-        <v>66</v>
-      </c>
-      <c r="B72" s="1" t="s">
-        <v>99</v>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="B72" s="1"/>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2">
+      <c r="A74" t="s">
+        <v>62</v>
+      </c>
+      <c r="B74" s="1"/>
+    </row>
+    <row r="75" spans="1:2">
+      <c r="A75" t="s">
+        <v>63</v>
+      </c>
+      <c r="B75" s="1"/>
+    </row>
+    <row r="76" spans="1:2">
+      <c r="A76" t="s">
+        <v>64</v>
+      </c>
+      <c r="B76">
+        <v>11999</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2">
+      <c r="A77" t="s">
+        <v>65</v>
+      </c>
+      <c r="B77" s="1"/>
+    </row>
+    <row r="78" spans="1:2">
+      <c r="A78" t="s">
+        <v>66</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2">
+      <c r="A79" t="s">
         <v>97</v>
       </c>
-      <c r="B73" t="s">
+      <c r="B79" t="s">
         <v>98</v>
       </c>
     </row>
